--- a/itens.xlsx
+++ b/itens.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Victor Franco\Documents\GitHub\buppo-game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E8F394B-055A-4961-9F0B-D44B9D01F61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFCF784C-C99D-4BC3-B998-C58928A4B2F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{283F8FFC-B0F6-457D-965F-AA9C695C9921}"/>
   </bookViews>
